--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A22AAE4EF0BFDC4B82D1BA9630B51FA09086B8F1" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{EC19FB7D-B147-4869-915F-D453BC4C7578}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="141">
   <si>
     <t>49014</t>
   </si>
@@ -142,16 +148,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>AC26C2BBA9431ECD2983365A1CE24E21</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ingresos por Venta de Bienes, Prestación de Servicios y Otros Ingresos</t>
@@ -160,31 +157,22 @@
     <t>Ingresos por ventas de bienes y prestación de servicios</t>
   </si>
   <si>
-    <t>51024</t>
-  </si>
-  <si>
     <t>Ingresos Propios</t>
   </si>
   <si>
-    <t>Secretaría de Planeación y Finanzas del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>15/12/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/4to_Trimestre/Informacion%20Presupuestal/prsupuestal_4to_trimestre.pdf</t>
-  </si>
-  <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>936028F0E7ADD20455E9FD044AF6D10A</t>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Aprovechamientos</t>
   </si>
   <si>
     <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
@@ -193,7 +181,10 @@
     <t>Subsidios y Subvenciones</t>
   </si>
   <si>
-    <t>9758908</t>
+    <t>Recursos Estatales</t>
+  </si>
+  <si>
+    <t>58517</t>
   </si>
   <si>
     <t>Recursos Federales</t>
@@ -202,254 +193,262 @@
     <t>Subsecretaría de Educación Media Superior</t>
   </si>
   <si>
-    <t>14/12/2022</t>
-  </si>
-  <si>
-    <t>47D2C17C59D2C8E7E599A3A13E02BD2F</t>
-  </si>
-  <si>
-    <t>Productos</t>
-  </si>
-  <si>
-    <t>81526.98</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>30/11/2022</t>
-  </si>
-  <si>
-    <t>894F04C9617B3595A08319D8CF9568C8</t>
-  </si>
-  <si>
-    <t>Derechos</t>
-  </si>
-  <si>
-    <t>Derechos por Prestación de Servicios</t>
-  </si>
-  <si>
-    <t>435422.08</t>
-  </si>
-  <si>
-    <t>B25D6B4EB8040E8DE9C2EA4B25F9AACA</t>
-  </si>
-  <si>
-    <t>38179</t>
-  </si>
-  <si>
-    <t>22/11/2022</t>
-  </si>
-  <si>
-    <t>C508969F1C8754E4C58E7687B5CA1722</t>
-  </si>
-  <si>
-    <t>1652974</t>
-  </si>
-  <si>
-    <t>15/11/2022</t>
-  </si>
-  <si>
-    <t>1508C9A800966561DF37A060986E1C03</t>
-  </si>
-  <si>
-    <t>Aprovechamientos</t>
-  </si>
-  <si>
-    <t>5424750.45</t>
-  </si>
-  <si>
-    <t>B0087A8464D5176AB0A8DED11F81553E</t>
-  </si>
-  <si>
-    <t>109839.05</t>
-  </si>
-  <si>
-    <t>C6C8B584138C98CBC36A9479DA301D07</t>
-  </si>
-  <si>
-    <t>-4268865.57</t>
-  </si>
-  <si>
-    <t>0406F5A0F2E25052BC3B3BD9D8AF9937</t>
-  </si>
-  <si>
-    <t>2114</t>
-  </si>
-  <si>
-    <t>28/12/2022</t>
-  </si>
-  <si>
-    <t>1FC06D303D9EDDD84806F6634E7A86D4</t>
-  </si>
-  <si>
-    <t>9097</t>
-  </si>
-  <si>
-    <t>23/12/2022</t>
-  </si>
-  <si>
-    <t>4F4511486D85CB08AD8569D0ED7C5A7F</t>
-  </si>
-  <si>
-    <t>Participaciones, Aportaciones, Convenios, Incentivos Derivados de la Colaboración Fiscal y
-Fondos Distintos de Aportaciones</t>
-  </si>
-  <si>
-    <t>Aportaciones</t>
-  </si>
-  <si>
-    <t>105662</t>
-  </si>
-  <si>
-    <t>Transferencias Federales Etiquetadas</t>
-  </si>
-  <si>
-    <t>5E967A4D3FE7F647CA739AFF90AF076E</t>
-  </si>
-  <si>
-    <t>195208</t>
-  </si>
-  <si>
-    <t>11/11/2022</t>
-  </si>
-  <si>
-    <t>AF87930424F1B72B0A81F67AD1105C8B</t>
-  </si>
-  <si>
-    <t>49557301</t>
-  </si>
-  <si>
-    <t>69441860B8C20CB0EDA655FFC0634F1E</t>
-  </si>
-  <si>
-    <t>63705.63</t>
-  </si>
-  <si>
-    <t>31/10/2022</t>
-  </si>
-  <si>
-    <t>1F30FB250C71E13B1FC28D00EB4A9DBA</t>
-  </si>
-  <si>
-    <t>670768.69</t>
-  </si>
-  <si>
-    <t>186A5B802822A6E19E8172581C87BB13</t>
-  </si>
-  <si>
-    <t>5D90FAE6A39FB82ABA9F6F1164A323F5</t>
-  </si>
-  <si>
-    <t>166667</t>
-  </si>
-  <si>
-    <t>7063CCA8A31049B0A20FE098F37868AA</t>
-  </si>
-  <si>
-    <t>115498.75</t>
-  </si>
-  <si>
-    <t>Recursos Estatales</t>
-  </si>
-  <si>
-    <t>20/10/2022</t>
-  </si>
-  <si>
-    <t>0A837A3E2071C2D8DC1BEBB3D0DFFD28</t>
-  </si>
-  <si>
-    <t>13019601.02</t>
-  </si>
-  <si>
-    <t>27/10/2022</t>
-  </si>
-  <si>
-    <t>F6772DC72BF4D2423F247397B7037A02</t>
-  </si>
-  <si>
-    <t>9905564.1</t>
-  </si>
-  <si>
-    <t>33BD6AC9048D2C51356F5BE2DC4DF775</t>
-  </si>
-  <si>
-    <t>A2A9C1414FE3193937B4B7CA066753CC</t>
-  </si>
-  <si>
-    <t>125000</t>
-  </si>
-  <si>
-    <t>992AAD35C42870FEFAFA00A093FF0621</t>
-  </si>
-  <si>
-    <t>195207</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>E4BE4267982B6C9DEA62BD07A4BDEB91</t>
-  </si>
-  <si>
-    <t>29987849</t>
-  </si>
-  <si>
-    <t>D466AF28F61A2A2B946D4215BE0B38C5</t>
-  </si>
-  <si>
-    <t>105666</t>
-  </si>
-  <si>
-    <t>09/12/2022</t>
-  </si>
-  <si>
-    <t>51EE9E15A550F20662266169A78B64C3</t>
-  </si>
-  <si>
-    <t>166663</t>
-  </si>
-  <si>
-    <t>CE11CA6C29135B428AC69FA4AE0C77BC</t>
-  </si>
-  <si>
-    <t>227004.75</t>
-  </si>
-  <si>
-    <t>B5C2366F388FA6E11710C183F96F342D</t>
-  </si>
-  <si>
-    <t>16810893.96</t>
-  </si>
-  <si>
-    <t>91421F51A0A471228A066279D0B78110</t>
-  </si>
-  <si>
-    <t>60130</t>
-  </si>
-  <si>
-    <t>DA26D6891F6473B1034A3E37F0D13508</t>
-  </si>
-  <si>
-    <t>4B55383350B7FB1F04F4ED41CAC4C925</t>
-  </si>
-  <si>
-    <t>149562.75</t>
-  </si>
-  <si>
-    <t>C728EA6B6B80D25AFB316EBD4CCDF14D</t>
-  </si>
-  <si>
-    <t>5017869.5</t>
-  </si>
-  <si>
-    <t>22309EBD58F6FA1B12D2F3AA184D97F9</t>
+    <t>EF60581F019481B4CE73F71CC303AED6</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>31284060</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/4to%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>15/01/2024</t>
+  </si>
+  <si>
+    <t>41DAAEB75319A578EABE25C7183ADE56</t>
+  </si>
+  <si>
+    <t>203970</t>
+  </si>
+  <si>
+    <t>16/10/2023</t>
+  </si>
+  <si>
+    <t>599A31C8C008D7AF6C8FB9A9E8D9D565</t>
+  </si>
+  <si>
+    <t>5261009.75</t>
+  </si>
+  <si>
+    <t>Secretaría de Finanzas del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>19/10/2023</t>
+  </si>
+  <si>
+    <t>F81A41A71E5EBAD491A947177EEC936B</t>
+  </si>
+  <si>
+    <t>5770129.75</t>
+  </si>
+  <si>
+    <t>377447D3B42AD4CF68EEEEF59423F368</t>
+  </si>
+  <si>
+    <t>5996564.25</t>
+  </si>
+  <si>
+    <t>25/10/2023</t>
+  </si>
+  <si>
+    <t>7E44756F86FD6E54601E375F7628421F</t>
+  </si>
+  <si>
+    <t>6505684.25</t>
+  </si>
+  <si>
+    <t>A6F94955B8F38EBFD4422A7F29D367FA</t>
+  </si>
+  <si>
+    <t>60918</t>
+  </si>
+  <si>
+    <t>78D74DEEABD1E2FAD61EFE6D4ADF47B7</t>
+  </si>
+  <si>
+    <t>1347053</t>
+  </si>
+  <si>
+    <t>CAEE2154A45AB8DC86608DFE1F92C5E6</t>
+  </si>
+  <si>
+    <t>E6D75EA458504461F60C6C2BC409914F</t>
+  </si>
+  <si>
+    <t>31623.02</t>
+  </si>
+  <si>
+    <t>31/10/2023</t>
+  </si>
+  <si>
+    <t>2D00B79F30DEF1E68BEBBFBE492A05CA</t>
+  </si>
+  <si>
+    <t>63547</t>
+  </si>
+  <si>
+    <t>53F81AA32C77FCA37B2D6F62E49EF7EA</t>
+  </si>
+  <si>
+    <t>203980</t>
+  </si>
+  <si>
+    <t>21/11/2023</t>
+  </si>
+  <si>
+    <t>4D16A6C883C69666B163D792A7C02A21</t>
+  </si>
+  <si>
+    <t>6297448.75</t>
+  </si>
+  <si>
+    <t>22/11/2023</t>
+  </si>
+  <si>
+    <t>1D78B3DC497A35D13E74D4C044D59DA2</t>
+  </si>
+  <si>
+    <t>4212026.25</t>
+  </si>
+  <si>
+    <t>16/11/2023</t>
+  </si>
+  <si>
+    <t>8662087293C297D1E1C711EA84467A06</t>
+  </si>
+  <si>
+    <t>5534051.25</t>
+  </si>
+  <si>
+    <t>D343F78C14F5C060FA04E2F6DA3B5D33</t>
+  </si>
+  <si>
+    <t>4975423.75</t>
+  </si>
+  <si>
+    <t>96EFC00967C5406F3F9A4A5F1BCA0BA7</t>
+  </si>
+  <si>
+    <t>153499</t>
+  </si>
+  <si>
+    <t>F0629E217A6CD71D4AFB570A01E53A6A</t>
+  </si>
+  <si>
+    <t>28772</t>
+  </si>
+  <si>
+    <t>4080F74496F81E037FD68906E2DAEB62</t>
+  </si>
+  <si>
+    <t>100672.35</t>
+  </si>
+  <si>
+    <t>30/11/2023</t>
+  </si>
+  <si>
+    <t>2D2AAB7944E2D5DFF4DB3D4EE8142A72</t>
+  </si>
+  <si>
+    <t>51758936</t>
+  </si>
+  <si>
+    <t>20/12/2023</t>
+  </si>
+  <si>
+    <t>A1C9D7644AD398B76290656594F3B5E2</t>
+  </si>
+  <si>
+    <t>35541.5</t>
+  </si>
+  <si>
+    <t>81FE1FC02E01C5E4231D20C7D8D5A8E9</t>
+  </si>
+  <si>
+    <t>12055022.5</t>
+  </si>
+  <si>
+    <t>29/12/2023</t>
+  </si>
+  <si>
+    <t>3C5612397E98ABA4446D457E5E56CFF6</t>
+  </si>
+  <si>
+    <t>89152.5</t>
+  </si>
+  <si>
+    <t>26/12/2023</t>
+  </si>
+  <si>
+    <t>8074CA87253CB03FB4571C887DC9C099</t>
+  </si>
+  <si>
+    <t>26628378</t>
+  </si>
+  <si>
+    <t>11/12/2023</t>
+  </si>
+  <si>
+    <t>E84FC92880ACC000EEB7E8C481962A45</t>
+  </si>
+  <si>
+    <t>11769076.5</t>
+  </si>
+  <si>
+    <t>27/12/2023</t>
+  </si>
+  <si>
+    <t>A5C489CEFBBD090BD9A87B99F38050AB</t>
+  </si>
+  <si>
+    <t>3294619.61</t>
+  </si>
+  <si>
+    <t>CA589305DDE0C33F7CC61825B3AD9A43</t>
+  </si>
+  <si>
+    <t>40383757</t>
+  </si>
+  <si>
+    <t>13/12/2023</t>
+  </si>
+  <si>
+    <t>3C424BEE1C23D3539E2E7328832A16C1</t>
+  </si>
+  <si>
+    <t>230941</t>
+  </si>
+  <si>
+    <t>2F0355B77567AAB9F66E2E352DF8DFDF</t>
+  </si>
+  <si>
+    <t>BD783F8AF44A4D5FEEC906AEA99F11A0</t>
+  </si>
+  <si>
+    <t>24420</t>
+  </si>
+  <si>
+    <t>9586D022D45CB1C914CEE85750F1F020</t>
+  </si>
+  <si>
+    <t>51010.28</t>
+  </si>
+  <si>
+    <t>BF21206155054CA6A0A4247508D6264B</t>
+  </si>
+  <si>
+    <t>219939.24</t>
+  </si>
+  <si>
+    <t>B023DAA1B56A54F5B6580B4B2A968A87</t>
+  </si>
+  <si>
+    <t>21410</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -545,6 +544,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -560,44 +562,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -625,14 +627,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -660,6 +679,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -671,185 +707,161 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="185.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -1046,284 +1058,284 @@
     </row>
     <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="K13" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1331,1315 +1343,1268 @@
         <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="K24" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="G25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="K31" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="K34" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="G37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="I37" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="I38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="I39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="I40" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
